--- a/basedatos_partidas/salida/descompuestos/14.04.01.020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/14.04.01.020.xlsx
@@ -662,10 +662,10 @@
         <v>0.1</v>
       </c>
       <c r="G14" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>19.46</v>
+        <v>19.54</v>
       </c>
     </row>
     <row r="16">
@@ -847,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>24.16</v>
+        <v>24.24</v>
       </c>
       <c r="H25" t="n">
         <v>0.24</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>24.4</v>
+        <v>24.48</v>
       </c>
     </row>
   </sheetData>
